--- a/Depth-Anything-V2/record.xlsx
+++ b/Depth-Anything-V2/record.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tkmco\study\Depth-Anything-V2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{214AC5F8-016F-4E7E-BA22-085136D2832F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FB2E757-2937-4B19-8AC1-689321415876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="610" windowWidth="35660" windowHeight="20270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1520" yWindow="610" windowWidth="35660" windowHeight="20270" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="sd" sheetId="2" r:id="rId2"/>
+    <sheet name="実行時間" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>nanameuse</t>
   </si>
@@ -74,6 +75,63 @@
     <t>非接触</t>
     <rPh sb="0" eb="3">
       <t>ヒセッショク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>深度推定時間</t>
+    <rPh sb="0" eb="2">
+      <t>シンド</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>スイテイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カラー化</t>
+    <rPh sb="3" eb="4">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大きさ</t>
+    <rPh sb="0" eb="1">
+      <t>オオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>maue画像に対して</t>
+    <rPh sb="4" eb="6">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>タイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>単位は秒</t>
+    <rPh sb="0" eb="2">
+      <t>タンイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ビョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>試行回数は一回</t>
+    <rPh sb="0" eb="4">
+      <t>シコウカイスウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>イチカイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -142,7 +200,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -155,6 +213,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -37377,4 +37444,94 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D99C12D0-AE31-4140-B479-AF7A6E8D1219}">
+  <dimension ref="B1:G7"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="2" width="13.5" customWidth="1"/>
+    <col min="3" max="3" width="21.83203125" customWidth="1"/>
+    <col min="4" max="4" width="17.58203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:7" ht="36" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B1" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="7"/>
+      <c r="D1" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="8"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B4" s="6">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>0.22441989999970199</v>
+      </c>
+      <c r="D4">
+        <v>0.16450309999891</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="C5">
+        <v>0.21543369999926601</v>
+      </c>
+      <c r="D5">
+        <v>8.9348800000152495E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B6" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="C6">
+        <v>0.200979799999913</v>
+      </c>
+      <c r="D6">
+        <v>3.7327500000173999E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="C7">
+        <v>0.19178880000072199</v>
+      </c>
+      <c r="D7">
+        <v>1.36144999996759E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Depth-Anything-V2/record.xlsx
+++ b/Depth-Anything-V2/record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tkmco\study\Depth-Anything-V2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FB2E757-2937-4B19-8AC1-689321415876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63745A4D-0B12-40C3-8FE9-6755265F626C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1520" yWindow="610" windowWidth="35660" windowHeight="20270" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>nanameuse</t>
   </si>
@@ -132,6 +132,13 @@
     </rPh>
     <rPh sb="5" eb="7">
       <t>イチカイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>解像度(dpi)</t>
+    <rPh sb="0" eb="3">
+      <t>カイゾウド</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -37448,7 +37455,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D99C12D0-AE31-4140-B479-AF7A6E8D1219}">
-  <dimension ref="B1:G7"/>
+  <dimension ref="B1:G11"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="13.5" customWidth="1"/>
@@ -37525,6 +37532,27 @@
         <v>1.36144999996759E-2</v>
       </c>
     </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B10" s="6">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="B11" s="6">
+        <v>0.36</v>
+      </c>
+      <c r="C11">
+        <v>0.202689400000963</v>
+      </c>
+      <c r="D11">
+        <v>4.75609999848529E-2</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B1:C1"/>
